--- a/static/example_excel/import.xlsx
+++ b/static/example_excel/import.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LocalAdm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BE39F1-D95B-4858-9747-033460D55F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B58A6EA-7DF8-4384-90E5-CE28DB3BA518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27765" yWindow="4470" windowWidth="27390" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="420" yWindow="2655" windowWidth="27390" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Студенти" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Дата народження</t>
   </si>
@@ -79,6 +90,12 @@
   </si>
   <si>
     <t>0991234568</t>
+  </si>
+  <si>
+    <t>Стать</t>
+  </si>
+  <si>
+    <t>Ч</t>
   </si>
 </sst>
 </file>
@@ -86,14 +103,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -133,17 +158,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -446,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -461,7 +487,7 @@
     <col min="10" max="10" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -492,8 +518,11 @@
       <c r="J1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="K1" s="8" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -522,8 +551,11 @@
       <c r="J2" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="6"/>
@@ -535,13 +567,13 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G10" s="2"/>
     </row>
   </sheetData>
